--- a/data/enge/AY/Output/base.ENGE_1993a2024_wider.id.xlsx
+++ b/data/enge/AY/Output/base.ENGE_1993a2024_wider.id.xlsx
@@ -29274,7 +29274,7 @@
         <v>33</v>
       </c>
       <c r="E434" t="n">
-        <v>630.28</v>
+        <v>27764.6</v>
       </c>
       <c r="F434" t="n">
         <v>9541.18</v>
@@ -29333,7 +29333,7 @@
         <v>31</v>
       </c>
       <c r="E435" t="n">
-        <v>13140.46</v>
+        <v>9.1</v>
       </c>
       <c r="F435"/>
       <c r="G435"/>
@@ -30373,7 +30373,7 @@
         <v>62</v>
       </c>
       <c r="D454" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="E454" t="n">
         <v>416.2</v>
@@ -30543,7 +30543,7 @@
         <v>33</v>
       </c>
       <c r="E457" t="n">
-        <v>2166.32</v>
+        <v>31031.7</v>
       </c>
       <c r="F457" t="n">
         <v>10400.33</v>
@@ -30601,7 +30601,9 @@
       <c r="D458" t="s">
         <v>31</v>
       </c>
-      <c r="E458"/>
+      <c r="E458" t="n">
+        <v>8</v>
+      </c>
       <c r="F458"/>
       <c r="G458"/>
       <c r="H458"/>
@@ -31640,7 +31642,7 @@
         <v>62</v>
       </c>
       <c r="D477" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="E477" t="n">
         <v>501</v>
